--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_18.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_18.xlsx
@@ -667,7 +667,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -730,7 +730,7 @@
     <t>Di Gregorio</t>
   </si>
   <si>
-    <t>D'ambrosio</t>
+    <t>D'Ambrosio</t>
   </si>
   <si>
     <t>Pereira P.</t>
@@ -838,7 +838,7 @@
     <t>Mancini</t>
   </si>
   <si>
-    <t>N'dicka</t>
+    <t>N'Dicka</t>
   </si>
   <si>
     <t>Llorente D.</t>
